--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T06:07:49+00:00</t>
+    <t>2023-11-14T21:40:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
+++ b/CodeSystem-WHO-DDCC-icao-lab-test-origin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
